--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_05/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_05/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>28.61320119289024</v>
+        <v>99.99999999639226</v>
       </c>
       <c r="B2" t="n">
-        <v>66.38788569365376</v>
+        <v>77.673166024249</v>
       </c>
       <c r="C2" t="n">
-        <v>33.66940640593264</v>
+        <v>38.57334075845323</v>
       </c>
       <c r="D2" t="n">
-        <v>5.163385524885169</v>
+        <v>6.202959804580311</v>
       </c>
       <c r="E2" t="n">
-        <v>2.947543769747156</v>
+        <v>3.813086748414553</v>
       </c>
       <c r="F2" t="n">
-        <v>1.664982179631355</v>
+        <v>7.822280449164157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2611802847005887</v>
+        <v>0.003376053954492883</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0006819025657234315</v>
+        <v>-0.9694706065450763</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3932665548668889</v>
+        <v>-0.9739583286915682</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3743303368709799</v>
+        <v>-0.993501906862721</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.003601558056665211</v>
+        <v>-0.001509159618822936</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6612935120439357</v>
+        <v>-0.5874999999742948</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08093483522652703</v>
+        <v>-0.0004461769724194153</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999964690801</v>
+        <v>30.1175187685287</v>
       </c>
       <c r="B3" t="n">
-        <v>60.21097557354022</v>
+        <v>64.70141556596151</v>
       </c>
       <c r="C3" t="n">
-        <v>33.68592891059157</v>
+        <v>38.58102384260085</v>
       </c>
       <c r="D3" t="n">
-        <v>5.988788295853968</v>
+        <v>5.568451495717177</v>
       </c>
       <c r="E3" t="n">
-        <v>2.944115188256304</v>
+        <v>4.99898833757351</v>
       </c>
       <c r="F3" t="n">
-        <v>7.742218379255775</v>
+        <v>1.745345866891513</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003427726249707997</v>
+        <v>0.2120987688860624</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9731096688032184</v>
+        <v>-0.01701362564796432</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9769139011000338</v>
+        <v>-0.4007305560416317</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9944751783239295</v>
+        <v>-0.3890936780355116</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0001436618075705646</v>
+        <v>-0.01404251871382479</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069703564143</v>
+        <v>-0.6257344923033044</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.08423204826175289</v>
+        <v>-0.002238896606864549</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99999964690801</v>
+        <v>61.28302321863797</v>
       </c>
       <c r="B4" t="n">
-        <v>60.21097557354022</v>
+        <v>111.6609726863251</v>
       </c>
       <c r="C4" t="n">
-        <v>33.68592891059157</v>
+        <v>40.00029196883234</v>
       </c>
       <c r="D4" t="n">
-        <v>5.988788295853968</v>
+        <v>9.641652738126744</v>
       </c>
       <c r="E4" t="n">
-        <v>2.947832418914891</v>
+        <v>4.82582211815085</v>
       </c>
       <c r="F4" t="n">
-        <v>7.742218379255775</v>
+        <v>3.869540636308824</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003427726249707997</v>
+        <v>0.01739176927726998</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9731096688032184</v>
+        <v>-0.8759729445503651</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9769139011000338</v>
+        <v>-0.8961417212665922</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9944751783239295</v>
+        <v>-0.9595613731477005</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0001436618075705646</v>
+        <v>-0.01236923092940959</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220069703564143</v>
+        <v>-0.3116415404327956</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08423204826175289</v>
+        <v>-0.3334014593942128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>37.02610134140065</v>
+        <v>32.1853942092535</v>
       </c>
       <c r="B5" t="n">
-        <v>62.49350569112512</v>
+        <v>62.23934801405901</v>
       </c>
       <c r="C5" t="n">
-        <v>33.71387947044471</v>
+        <v>38.58130910462432</v>
       </c>
       <c r="D5" t="n">
-        <v>5.154557857188031</v>
+        <v>5.307025795773247</v>
       </c>
       <c r="E5" t="n">
-        <v>2.440745543063269</v>
+        <v>4.997321102688735</v>
       </c>
       <c r="F5" t="n">
-        <v>2.228203097784903</v>
+        <v>1.865359273790182</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09835167587787556</v>
+        <v>0.1640729674448401</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.534814092770747</v>
+        <v>-0.1934990220333347</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6698299822020317</v>
+        <v>-0.4866002474577102</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.772729437394825</v>
+        <v>-0.5302703012413843</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.05664763037150827</v>
+        <v>-0.008573228946888285</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6679896323734175</v>
+        <v>-0.6386587138078343</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.089809831545343</v>
+        <v>-0.002305457745675615</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>63.64333827865001</v>
+        <v>31.05860940015686</v>
       </c>
       <c r="B6" t="n">
-        <v>156.4052284185835</v>
+        <v>64.70161900975965</v>
       </c>
       <c r="C6" t="n">
-        <v>35.28453418470698</v>
+        <v>38.58069647677942</v>
       </c>
       <c r="D6" t="n">
-        <v>9.799387389653152</v>
+        <v>5.56838347747892</v>
       </c>
       <c r="E6" t="n">
-        <v>4.030284176804938</v>
+        <v>3.728875962371099</v>
       </c>
       <c r="F6" t="n">
-        <v>4.080351756336622</v>
+        <v>1.813157604246087</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0155535887049848</v>
+        <v>0.1884666946018046</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9027418858244897</v>
+        <v>-0.1030553729675248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9183987927550714</v>
+        <v>-0.4419803667387279</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9705624696791054</v>
+        <v>-0.4590228187205311</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.007938958689599694</v>
+        <v>-0.02080198423913277</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.350420174787698</v>
+        <v>-0.6267634010322058</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06698020211493287</v>
+        <v>-0.002162511248529758</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82.27118150192895</v>
+        <v>78.31763009948033</v>
       </c>
       <c r="B7" t="n">
-        <v>144.6975948333503</v>
+        <v>80.68959366423312</v>
       </c>
       <c r="C7" t="n">
-        <v>33.66915659875096</v>
+        <v>38.60022973339967</v>
       </c>
       <c r="D7" t="n">
-        <v>8.235375063132111</v>
+        <v>8.285699739123059</v>
       </c>
       <c r="E7" t="n">
-        <v>2.81042119257841</v>
+        <v>4.486194158072847</v>
       </c>
       <c r="F7" t="n">
-        <v>5.74646654841393</v>
+        <v>5.343086764943998</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006402021728053269</v>
+        <v>0.007393052047570744</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9535549526824211</v>
+        <v>-0.9397287293135227</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9615910731868589</v>
+        <v>-0.9518063149441151</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9887976461871059</v>
+        <v>-0.9844058853023692</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0119928856761493</v>
+        <v>-0.02268887808211537</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4895714625839888</v>
+        <v>-0.4476976701024499</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08088498397741359</v>
+        <v>-0.006720271126589294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>31.94313466362233</v>
+        <v>72.97274259913549</v>
       </c>
       <c r="B8" t="n">
-        <v>63.19821613767584</v>
+        <v>88.55250409597305</v>
       </c>
       <c r="C8" t="n">
-        <v>33.71249076656746</v>
+        <v>39.05963384403758</v>
       </c>
       <c r="D8" t="n">
-        <v>5.015564033050019</v>
+        <v>8.655299395013664</v>
       </c>
       <c r="E8" t="n">
-        <v>4.609364310117338</v>
+        <v>4.221939794076166</v>
       </c>
       <c r="F8" t="n">
-        <v>1.872242144769734</v>
+        <v>4.828965056245629</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1712930692075826</v>
+        <v>0.009394284685572275</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2796745046581756</v>
+        <v>-0.9261896254646027</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5305370700803548</v>
+        <v>-0.9394716025942884</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5946947684195154</v>
+        <v>-0.9796933800820529</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.007930354423857465</v>
+        <v>-0.008795888247899288</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6618504715148099</v>
+        <v>-0.4086131802561782</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08953270331202329</v>
+        <v>-0.1139145636087686</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96.51561208147103</v>
+        <v>30.62723109590814</v>
       </c>
       <c r="B9" t="n">
-        <v>157.0604303632336</v>
+        <v>64.55645209316435</v>
       </c>
       <c r="C9" t="n">
-        <v>33.68762269298794</v>
+        <v>38.58762798134241</v>
       </c>
       <c r="D9" t="n">
-        <v>6.708664717387216</v>
+        <v>5.522253041711779</v>
       </c>
       <c r="E9" t="n">
-        <v>4.220945845846368</v>
+        <v>3.510265938943733</v>
       </c>
       <c r="F9" t="n">
-        <v>7.34900849049589</v>
+        <v>1.776322894690945</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003831016057355284</v>
+        <v>0.1987781598600734</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9703296601751019</v>
+        <v>-0.06496786666882121</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9746320619543055</v>
+        <v>-0.4235942754114299</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9937276677486135</v>
+        <v>-0.4283504416985979</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.06742536611938561</v>
+        <v>-0.01904816406487627</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.595978352276463</v>
+        <v>-0.6289201943494259</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08457005763208982</v>
+        <v>-0.003779862313228882</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>77.39093268832593</v>
+        <v>43.55786954725095</v>
       </c>
       <c r="B10" t="n">
-        <v>154.0654600034947</v>
+        <v>100.3009091305739</v>
       </c>
       <c r="C10" t="n">
-        <v>34.34359502212836</v>
+        <v>38.58938926958736</v>
       </c>
       <c r="D10" t="n">
-        <v>9.760690143738532</v>
+        <v>7.353497911963446</v>
       </c>
       <c r="E10" t="n">
-        <v>4.272032410423496</v>
+        <v>3.830233828411214</v>
       </c>
       <c r="F10" t="n">
-        <v>5.408096709604847</v>
+        <v>2.682017841553826</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00793419627117793</v>
+        <v>0.05496415736844878</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9445918113560664</v>
+        <v>-0.6677686652739149</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9548082138586363</v>
+        <v>-0.7497587066396795</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9858852963087066</v>
+        <v>-0.8536667889439089</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2216668526633222</v>
+        <v>-0.05584736561060053</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4531156636469155</v>
+        <v>-0.5258665071325892</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1384485400432036</v>
+        <v>-0.004190829570384358</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>38.65489526763078</v>
+        <v>32.96821643458235</v>
       </c>
       <c r="B11" t="n">
-        <v>66.61397980383511</v>
+        <v>84.25045823054185</v>
       </c>
       <c r="C11" t="n">
-        <v>33.66940640593264</v>
+        <v>38.58056321223956</v>
       </c>
       <c r="D11" t="n">
-        <v>5.177119291904771</v>
+        <v>5.539510390664928</v>
       </c>
       <c r="E11" t="n">
-        <v>2.963728815043942</v>
+        <v>4.054799913755177</v>
       </c>
       <c r="F11" t="n">
-        <v>2.374267381605766</v>
+        <v>1.953687684375599</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08367816415939645</v>
+        <v>0.1499830332870968</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5904655454815859</v>
+        <v>-0.2470113941875177</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7027577455315928</v>
+        <v>-0.5133009562404043</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8079792343314096</v>
+        <v>-0.5701814354673175</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1522572103791208</v>
+        <v>-0.05383499231837745</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6781289692106197</v>
+        <v>-0.6332487850803327</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.08093483522652703</v>
+        <v>-0.002131416189230378</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>84.95190227343802</v>
+        <v>42.32857309078809</v>
       </c>
       <c r="B12" t="n">
-        <v>151.5949116771393</v>
+        <v>81.54926812883411</v>
       </c>
       <c r="C12" t="n">
-        <v>35.92062738913387</v>
+        <v>38.59715765275742</v>
       </c>
       <c r="D12" t="n">
-        <v>7.664148856971746</v>
+        <v>7.272466569729463</v>
       </c>
       <c r="E12" t="n">
-        <v>2.977621716376423</v>
+        <v>3.74654992334587</v>
       </c>
       <c r="F12" t="n">
-        <v>6.024162190490356</v>
+        <v>2.57283919816522</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005759252712624827</v>
+        <v>0.06108757637494982</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9575889337179464</v>
+        <v>-0.63848285509645</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9646370291617937</v>
+        <v>-0.7313131244532695</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9900446302893715</v>
+        <v>-0.8363939455567891</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.005668556521443575</v>
+        <v>-0.004754892147511242</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5095966336736611</v>
+        <v>-0.5180809629083245</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.002367916453655874</v>
+        <v>-0.006003452310064522</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>30.42842378501554</v>
+        <v>92.84367574281298</v>
       </c>
       <c r="B13" t="n">
-        <v>64.33305441679752</v>
+        <v>111.1836289556671</v>
       </c>
       <c r="C13" t="n">
-        <v>33.67086608065684</v>
+        <v>39.07504010410592</v>
       </c>
       <c r="D13" t="n">
-        <v>5.002288602675328</v>
+        <v>7.216705101079031</v>
       </c>
       <c r="E13" t="n">
-        <v>3.16620550262077</v>
+        <v>3.995584140574317</v>
       </c>
       <c r="F13" t="n">
-        <v>1.774871380513985</v>
+        <v>6.981360363588396</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2059882234423133</v>
+        <v>0.004260241930473768</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.167951839622368</v>
+        <v>-0.9624178468845043</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4740583470343868</v>
+        <v>-0.9683532362990122</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5093854931389833</v>
+        <v>-0.9914982950214848</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.008713922702065214</v>
+        <v>-0.07324213911646468</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6688924336865162</v>
+        <v>-0.5365111896675425</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08122612632476901</v>
+        <v>-0.1175093576247158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>91.82201762387911</v>
+        <v>38.26385556589153</v>
       </c>
       <c r="B14" t="n">
-        <v>73.23980309911411</v>
+        <v>75.06497118358642</v>
       </c>
       <c r="C14" t="n">
-        <v>33.67331431036536</v>
+        <v>39.13447618624378</v>
       </c>
       <c r="D14" t="n">
-        <v>7.343683989944723</v>
+        <v>5.319314095435234</v>
       </c>
       <c r="E14" t="n">
-        <v>2.864427344895908</v>
+        <v>4.904564921926079</v>
       </c>
       <c r="F14" t="n">
-        <v>6.8053000808444</v>
+        <v>2.380609849931338</v>
       </c>
       <c r="G14" t="n">
-        <v>0.004484975097353242</v>
+        <v>0.08528248533839153</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9659082239249818</v>
+        <v>-0.5161971592866627</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9710852142644452</v>
+        <v>-0.6588124607973668</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.992495439258852</v>
+        <v>-0.7608494039664035</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.068652631939234</v>
+        <v>-0.2126133671151082</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5609168743941897</v>
+        <v>-0.6646916424224809</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08171469237905631</v>
+        <v>-0.1313777767902165</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>32.67229928082579</v>
+        <v>37.72557682709427</v>
       </c>
       <c r="B15" t="n">
-        <v>62.94715211876795</v>
+        <v>69.77264993461168</v>
       </c>
       <c r="C15" t="n">
-        <v>33.71485076192284</v>
+        <v>38.58543172292429</v>
       </c>
       <c r="D15" t="n">
-        <v>5.065422613547768</v>
+        <v>5.00213288665655</v>
       </c>
       <c r="E15" t="n">
-        <v>2.847791868904386</v>
+        <v>3.642812310062307</v>
       </c>
       <c r="F15" t="n">
-        <v>1.919282220921589</v>
+        <v>2.284670345620899</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1573520267178348</v>
+        <v>0.08968027935350367</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3262578093691852</v>
+        <v>-0.4956971818642672</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5547865748600752</v>
+        <v>-0.6471142407548074</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6290116780987618</v>
+        <v>-0.747442486315562</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.004490351467770343</v>
+        <v>-0.07103802573531494</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6580828695265031</v>
+        <v>-0.6614956124108722</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.09000366141489398</v>
+        <v>-0.003267402015667414</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>29.57622164228966</v>
+        <v>57.88924913658877</v>
       </c>
       <c r="B16" t="n">
-        <v>64.80140610832167</v>
+        <v>107.7379052550964</v>
       </c>
       <c r="C16" t="n">
-        <v>33.66944145721372</v>
+        <v>39.9628263225171</v>
       </c>
       <c r="D16" t="n">
-        <v>5.061538120935018</v>
+        <v>10.08735822377232</v>
       </c>
       <c r="E16" t="n">
-        <v>2.947544545046119</v>
+        <v>4.962132047732061</v>
       </c>
       <c r="F16" t="n">
-        <v>1.730584072197634</v>
+        <v>3.638625005633315</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2296000729703262</v>
+        <v>0.02141777724110448</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.09465508226997077</v>
+        <v>-0.8553231840784543</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4381570046935783</v>
+        <v>-0.8804072510733254</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4512812415255416</v>
+        <v>-0.9509181544706622</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.04865091425388186</v>
+        <v>-0.07059838437131438</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6706902867443031</v>
+        <v>-0.2983151343113053</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.08094183002200571</v>
+        <v>-0.3246594752539898</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56.01402355076748</v>
+        <v>79.84825973013416</v>
       </c>
       <c r="B17" t="n">
-        <v>60.93100407249978</v>
+        <v>79.55074419401511</v>
       </c>
       <c r="C17" t="n">
-        <v>31.40313717496454</v>
+        <v>38.5880427766667</v>
       </c>
       <c r="D17" t="n">
-        <v>5.964726984616892</v>
+        <v>8.145421956176804</v>
       </c>
       <c r="E17" t="n">
-        <v>3.148265061444391</v>
+        <v>3.943449740349536</v>
       </c>
       <c r="F17" t="n">
-        <v>3.814169770809447</v>
+        <v>5.496843332714525</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0221727353201748</v>
+        <v>0.00693000780003957</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8616937170945448</v>
+        <v>-0.942967245217322</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.885850141397119</v>
+        <v>-0.9543955156523609</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9539151462682093</v>
+        <v>-0.9854866495309104</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1540285349324467</v>
+        <v>-0.02311128320573436</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5929122744046796</v>
+        <v>-0.458890399276606</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1100477450653516</v>
+        <v>-0.003876647888896995</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36.1608194654932</v>
+        <v>35.3407083895827</v>
       </c>
       <c r="B18" t="n">
-        <v>62.86157704056058</v>
+        <v>81.05625791424099</v>
       </c>
       <c r="C18" t="n">
-        <v>33.7139828992705</v>
+        <v>38.59101964399316</v>
       </c>
       <c r="D18" t="n">
-        <v>5.13381363162606</v>
+        <v>5.173023987607904</v>
       </c>
       <c r="E18" t="n">
-        <v>2.43575159631611</v>
+        <v>4.833872572656714</v>
       </c>
       <c r="F18" t="n">
-        <v>2.151631639124373</v>
+        <v>2.100244665953731</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1075071694343064</v>
+        <v>0.1148517325565932</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5010662170879219</v>
+        <v>-0.3877718566204784</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6503790330223452</v>
+        <v>-0.5872370371866525</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7506603574709868</v>
+        <v>-0.6734285970340296</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.00119351518811151</v>
+        <v>-0.02320668641615282</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.662603202415849</v>
+        <v>-0.6473354560631472</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0898304716891753</v>
+        <v>-0.004571250265070631</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>39.80300661895328</v>
+        <v>90.03798311111493</v>
       </c>
       <c r="B19" t="n">
-        <v>68.01771227367715</v>
+        <v>71.03378376285583</v>
       </c>
       <c r="C19" t="n">
-        <v>33.68748115508259</v>
+        <v>38.75407228342215</v>
       </c>
       <c r="D19" t="n">
-        <v>5.060278877981273</v>
+        <v>7.410068578634437</v>
       </c>
       <c r="E19" t="n">
-        <v>3.286246843377875</v>
+        <v>3.947462407951313</v>
       </c>
       <c r="F19" t="n">
-        <v>2.465791029951779</v>
+        <v>6.634972943171516</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07494494835604339</v>
+        <v>0.004692209300198157</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6244691150995453</v>
+        <v>-0.9590373200188185</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7234705473467732</v>
+        <v>-0.9657526893962805</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8287880143720628</v>
+        <v>-0.9904962776541049</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1785444612776012</v>
+        <v>-0.03935983153930909</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6852760290873822</v>
+        <v>-0.5165206296666939</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.08454181248184464</v>
+        <v>-0.04261686613183477</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31.47431087916597</v>
+        <v>35.87931265310311</v>
       </c>
       <c r="B20" t="n">
-        <v>64.30132099808927</v>
+        <v>81.04679318452091</v>
       </c>
       <c r="C20" t="n">
-        <v>33.69102811584163</v>
+        <v>38.59101964399316</v>
       </c>
       <c r="D20" t="n">
-        <v>5.225531021601196</v>
+        <v>5.081832676647144</v>
       </c>
       <c r="E20" t="n">
-        <v>2.83784760819246</v>
+        <v>4.833872572656714</v>
       </c>
       <c r="F20" t="n">
-        <v>1.844293872507871</v>
+        <v>2.13435040577344</v>
       </c>
       <c r="G20" t="n">
-        <v>0.181723071400274</v>
+        <v>0.1083932767466068</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2470056024975168</v>
+        <v>-0.4147184163666232</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5137225051588916</v>
+        <v>-0.6019041629414322</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5700059855843165</v>
+        <v>-0.6923629988480124</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0004734893331098</v>
+        <v>-0.01321474721981726</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6570238819933646</v>
+        <v>-0.6505334188777997</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0852496401079554</v>
+        <v>-0.004571250265070631</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>29.11180254993788</v>
+        <v>52.17020612746367</v>
       </c>
       <c r="B21" t="n">
-        <v>64.80132978001767</v>
+        <v>91.92410045771103</v>
       </c>
       <c r="C21" t="n">
-        <v>33.67510017634422</v>
+        <v>38.58511210721307</v>
       </c>
       <c r="D21" t="n">
-        <v>5.004709904381086</v>
+        <v>6.956975273234533</v>
       </c>
       <c r="E21" t="n">
-        <v>2.954298420777869</v>
+        <v>3.656707240156149</v>
       </c>
       <c r="F21" t="n">
-        <v>1.701376069212855</v>
+        <v>3.41074283902634</v>
       </c>
       <c r="G21" t="n">
-        <v>0.243629627632247</v>
+        <v>0.02833598978176942</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.05121567961524494</v>
+        <v>-0.8048049205845278</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4172930601058233</v>
+        <v>-0.8426978229899761</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4161942680960543</v>
+        <v>-0.9274855572553913</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.06396476833316501</v>
+        <v>-0.1761607731422342</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6748848274693124</v>
+        <v>-0.5804113054739366</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.08207107784882724</v>
+        <v>-0.003192825016383322</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46.24043258635663</v>
+        <v>33.16980805155593</v>
       </c>
       <c r="B22" t="n">
-        <v>64.32687189133024</v>
+        <v>83.12736683277868</v>
       </c>
       <c r="C22" t="n">
-        <v>33.67099206931105</v>
+        <v>38.58056321223956</v>
       </c>
       <c r="D22" t="n">
-        <v>5.128990948135627</v>
+        <v>5.539171679887661</v>
       </c>
       <c r="E22" t="n">
-        <v>2.390590001743617</v>
+        <v>4.054799913755177</v>
       </c>
       <c r="F22" t="n">
-        <v>3.121568606899963</v>
+        <v>1.969353940217337</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04311742001092166</v>
+        <v>0.146537584713065</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7585948685259437</v>
+        <v>-0.2605361883360144</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8105690365339909</v>
+        <v>-0.5202222604394783</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9044385189646439</v>
+        <v>-0.5803895648244717</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5568492747912231</v>
+        <v>-0.06170356298698545</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.725349379802242</v>
+        <v>-0.6344457353061134</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.08125126848339044</v>
+        <v>-0.002131416189230378</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>88.70427687694215</v>
+        <v>39.98135454958734</v>
       </c>
       <c r="B23" t="n">
-        <v>129.413083968069</v>
+        <v>80.79531813345314</v>
       </c>
       <c r="C23" t="n">
-        <v>33.52754817121796</v>
+        <v>38.59737202795757</v>
       </c>
       <c r="D23" t="n">
-        <v>7.987793966857284</v>
+        <v>7.410068578634437</v>
       </c>
       <c r="E23" t="n">
-        <v>3.15665990373606</v>
+        <v>3.74654992334587</v>
       </c>
       <c r="F23" t="n">
-        <v>6.491907418982866</v>
+        <v>2.407487864636254</v>
       </c>
       <c r="G23" t="n">
-        <v>0.005020018066549642</v>
+        <v>0.07571524777456347</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9624242012091402</v>
+        <v>-0.5741656035783579</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9683279623602148</v>
+        <v>-0.6925595092172155</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9914862327793855</v>
+        <v>-0.7976267433220456</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1231055396483021</v>
+        <v>-0.0355717261841758</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5376271336146942</v>
+        <v>-0.5165423636639157</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.05682357553238362</v>
+        <v>-0.006053473190099495</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>87.49731063542892</v>
+        <v>36.90206235992835</v>
       </c>
       <c r="B24" t="n">
-        <v>139.3167272483054</v>
+        <v>76.81838004222092</v>
       </c>
       <c r="C24" t="n">
-        <v>33.67528895973985</v>
+        <v>38.584949671117</v>
       </c>
       <c r="D24" t="n">
-        <v>7.90419822422185</v>
+        <v>5.236345163328054</v>
       </c>
       <c r="E24" t="n">
-        <v>2.540525108852769</v>
+        <v>3.86487358512299</v>
       </c>
       <c r="F24" t="n">
-        <v>6.329085616215535</v>
+        <v>2.240727264805794</v>
       </c>
       <c r="G24" t="n">
-        <v>0.005239672889885216</v>
+        <v>0.09760758575869193</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9609623123408773</v>
+        <v>-0.4614360621181254</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9672084526239195</v>
+        <v>-0.627736633150888</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9910567518508268</v>
+        <v>-0.7244144918451215</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.07453562539668898</v>
+        <v>-0.1156791167452132</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5286110116289062</v>
+        <v>-0.6566059952620746</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.08210875125765667</v>
+        <v>-0.003154923260634546</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>43.46763933435592</v>
+        <v>34.50645475113528</v>
       </c>
       <c r="B25" t="n">
-        <v>65.05207626039147</v>
+        <v>81.32441543563472</v>
       </c>
       <c r="C25" t="n">
-        <v>30.75170216361335</v>
+        <v>38.60041071135036</v>
       </c>
       <c r="D25" t="n">
-        <v>5.17696514727218</v>
+        <v>5.213229474476067</v>
       </c>
       <c r="E25" t="n">
-        <v>2.812838448396816</v>
+        <v>3.748513719810681</v>
       </c>
       <c r="F25" t="n">
-        <v>2.851294837721016</v>
+        <v>2.036638309821304</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05414711407740981</v>
+        <v>0.125771560900291</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7103535075956774</v>
+        <v>-0.3427283541965951</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7780789905676954</v>
+        <v>-0.5631232885380569</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8784706437854941</v>
+        <v>-0.6411979193522805</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.358695015376999</v>
+        <v>-0.001152144225977601</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7080885806862809</v>
+        <v>-0.6423820750848657</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1673903177809566</v>
+        <v>-0.006762499315084852</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>41.7143620803724</v>
+        <v>86.72468081183378</v>
       </c>
       <c r="B26" t="n">
-        <v>65.82346082662062</v>
+        <v>108.8637667114302</v>
       </c>
       <c r="C26" t="n">
-        <v>33.66983658613036</v>
+        <v>38.58234348715875</v>
       </c>
       <c r="D26" t="n">
-        <v>5.018327296533398</v>
+        <v>8.068879263666746</v>
       </c>
       <c r="E26" t="n">
-        <v>2.513450224383978</v>
+        <v>4.978661437029576</v>
       </c>
       <c r="F26" t="n">
-        <v>2.64260086295217</v>
+        <v>6.297048233894092</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0629312523699086</v>
+        <v>0.00530369544436405</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6730620671991282</v>
+        <v>-0.9544330529965727</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7539323668032145</v>
+        <v>-0.9622381699667257</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.857435975157481</v>
+        <v>-0.9890842774435341</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2750264579803138</v>
+        <v>-0.1116062132944253</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6971743279003013</v>
+        <v>-0.4929133507843156</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.08102068151827828</v>
+        <v>-0.002546813670373516</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>72.13658581928465</v>
+        <v>41.15624352838906</v>
       </c>
       <c r="B27" t="n">
-        <v>128.7250223903593</v>
+        <v>100.3009091305739</v>
       </c>
       <c r="C27" t="n">
-        <v>33.71234889544057</v>
+        <v>38.58938926958736</v>
       </c>
       <c r="D27" t="n">
-        <v>9.735425602412004</v>
+        <v>7.361637844141493</v>
       </c>
       <c r="E27" t="n">
-        <v>2.645290965833329</v>
+        <v>3.895202549036321</v>
       </c>
       <c r="F27" t="n">
-        <v>4.831593995451514</v>
+        <v>2.491258671179012</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01003648045411117</v>
+        <v>0.06789582662851563</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.9322912224947515</v>
+        <v>-0.607100617875926</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9444627554548296</v>
+        <v>-0.7119484889169256</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9816779145872266</v>
+        <v>-0.8173296220955665</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1058261156128699</v>
+        <v>-0.0003981216427470522</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4138653261498833</v>
+        <v>-0.5106562090131306</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.08950439166445238</v>
+        <v>-0.004190829570384358</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>46.1541553142559</v>
+        <v>57.03345805986383</v>
       </c>
       <c r="B28" t="n">
-        <v>72.86224708609016</v>
+        <v>108.5834319153062</v>
       </c>
       <c r="C28" t="n">
-        <v>35.40247116894197</v>
+        <v>38.59344390237245</v>
       </c>
       <c r="D28" t="n">
-        <v>6.223655993778426</v>
+        <v>10.0859206403483</v>
       </c>
       <c r="E28" t="n">
-        <v>3.969691146141681</v>
+        <v>4.958026500805815</v>
       </c>
       <c r="F28" t="n">
-        <v>2.901194468204106</v>
+        <v>3.52541847246757</v>
       </c>
       <c r="G28" t="n">
-        <v>0.04458413863952371</v>
+        <v>0.02249869033396034</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7561415574601191</v>
+        <v>-0.8489611558332376</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8085454021309936</v>
+        <v>-0.8754934972737742</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9028145006769679</v>
+        <v>-0.948079978559055</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.006675998892041641</v>
+        <v>-0.04673705953827346</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.6014193960503992</v>
+        <v>-0.3027509354489787</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.04843903372014326</v>
+        <v>-0.005136910553570628</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28.61320119289024</v>
+        <v>36.50721251509251</v>
       </c>
       <c r="B29" t="n">
-        <v>65.65263683794772</v>
+        <v>77.05891517858379</v>
       </c>
       <c r="C29" t="n">
-        <v>33.66886668423228</v>
+        <v>38.58991657549853</v>
       </c>
       <c r="D29" t="n">
-        <v>5.17696514727218</v>
+        <v>5.001037246020532</v>
       </c>
       <c r="E29" t="n">
-        <v>2.947543769747156</v>
+        <v>4.036348928489714</v>
       </c>
       <c r="F29" t="n">
-        <v>1.678781560402798</v>
+        <v>2.17805767215008</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2608945526505079</v>
+        <v>0.1014640765644654</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0008470497296686724</v>
+        <v>-0.4441401763253487</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3933646209348708</v>
+        <v>-0.6181276658490779</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.3745571083392981</v>
+        <v>-0.7127013617243819</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.06699753084562975</v>
+        <v>-0.01157815496103361</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.6683297917904341</v>
+        <v>-0.6542615743083617</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.08082712895181011</v>
+        <v>-0.004313867616324157</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>34.43546012648667</v>
+        <v>30.23824753987741</v>
       </c>
       <c r="B30" t="n">
-        <v>66.38672950709268</v>
+        <v>64.55326792792329</v>
       </c>
       <c r="C30" t="n">
-        <v>33.687681943436</v>
+        <v>38.5807618243096</v>
       </c>
       <c r="D30" t="n">
-        <v>5.561032189679694</v>
+        <v>5.585826281350201</v>
       </c>
       <c r="E30" t="n">
-        <v>2.543257962191331</v>
+        <v>3.752684728275673</v>
       </c>
       <c r="F30" t="n">
-        <v>2.060460068094963</v>
+        <v>1.756037232897059</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1298044414247416</v>
+        <v>0.2088940319824201</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4229102542503679</v>
+        <v>-0.02863673241829483</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6065765781199774</v>
+        <v>-0.4062386403782904</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6975384219073354</v>
+        <v>-0.3986541801943665</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.06657203504939326</v>
+        <v>-0.02510112146772954</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.6518627402728635</v>
+        <v>-0.6264890471242338</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.08458188158697408</v>
+        <v>-0.002177759005574792</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>33.59323481849135</v>
+        <v>51.29003794134037</v>
       </c>
       <c r="B31" t="n">
-        <v>64.16636709371186</v>
+        <v>79.41576852890834</v>
       </c>
       <c r="C31" t="n">
-        <v>33.71244484920014</v>
+        <v>38.75411518478757</v>
       </c>
       <c r="D31" t="n">
-        <v>5.439282213424217</v>
+        <v>6.63808154061868</v>
       </c>
       <c r="E31" t="n">
-        <v>4.755877272689355</v>
+        <v>3.94742075963218</v>
       </c>
       <c r="F31" t="n">
-        <v>1.987319486341905</v>
+        <v>3.289693047721167</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1424027901263146</v>
+        <v>0.0300552811458348</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3790447502318104</v>
+        <v>-0.7949043327617927</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5827608355502691</v>
+        <v>-0.8355708455073024</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6667738217619704</v>
+        <v>-0.9226296464143153</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.01283383137725522</v>
+        <v>-0.07336492494586548</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.6491038665634624</v>
+        <v>-0.5748369069618222</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.08952354009220979</v>
+        <v>-0.04262687645043409</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>33.09576527681983</v>
+        <v>83.59152867084885</v>
       </c>
       <c r="B32" t="n">
-        <v>67.25244733011291</v>
+        <v>78.06003655860006</v>
       </c>
       <c r="C32" t="n">
-        <v>33.65151099455168</v>
+        <v>38.60061884188559</v>
       </c>
       <c r="D32" t="n">
-        <v>5.638820892317209</v>
+        <v>8.09269985263067</v>
       </c>
       <c r="E32" t="n">
-        <v>3.14250115056758</v>
+        <v>3.637447791211837</v>
       </c>
       <c r="F32" t="n">
-        <v>1.966094443622084</v>
+        <v>5.923210716011114</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1510880981834952</v>
+        <v>0.005969103095244237</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3506728069211507</v>
+        <v>-0.9494350646575163</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.567547958353953</v>
+        <v>-0.9585471554190867</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6463392179620168</v>
+        <v>-0.9875067824489849</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.02962433226665305</v>
+        <v>-0.04732841490742919</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.6435230619863191</v>
+        <v>-0.4705896417797979</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.07779158509947691</v>
+        <v>-0.006811063106638982</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>41.67811910867565</v>
+        <v>48.78702940430702</v>
       </c>
       <c r="B33" t="n">
-        <v>74.28767417040999</v>
+        <v>110.1334650980478</v>
       </c>
       <c r="C33" t="n">
-        <v>33.67301007792463</v>
+        <v>38.61344971965649</v>
       </c>
       <c r="D33" t="n">
-        <v>5.018327296533398</v>
+        <v>7.429909937226587</v>
       </c>
       <c r="E33" t="n">
-        <v>2.513450224383978</v>
+        <v>4.836410059706349</v>
       </c>
       <c r="F33" t="n">
-        <v>2.582622910319249</v>
+        <v>3.146978899615926</v>
       </c>
       <c r="G33" t="n">
-        <v>0.06330925155734511</v>
+        <v>0.03625534779670894</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6720676614383481</v>
+        <v>-0.7621384362572171</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.753256000447362</v>
+        <v>-0.8123691001368164</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.8568133936941645</v>
+        <v>-0.9058556336058815</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.05590143587364393</v>
+        <v>-0.198581106486807</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.67430462607202</v>
+        <v>-0.5589845195606111</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.08165398008452195</v>
+        <v>-0.009804934586512409</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>52.44659468423618</v>
+        <v>31.6683691979984</v>
       </c>
       <c r="B34" t="n">
-        <v>73.36357773998542</v>
+        <v>65.52099578080572</v>
       </c>
       <c r="C34" t="n">
-        <v>33.70937541413354</v>
+        <v>38.58093921942137</v>
       </c>
       <c r="D34" t="n">
-        <v>6.539931204604303</v>
+        <v>5.587168163923104</v>
       </c>
       <c r="E34" t="n">
-        <v>2.905814747121999</v>
+        <v>3.752684728275673</v>
       </c>
       <c r="F34" t="n">
-        <v>3.366225159517337</v>
+        <v>1.860505086855872</v>
       </c>
       <c r="G34" t="n">
-        <v>0.02826479859408817</v>
+        <v>0.1749672947278571</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8321472693408334</v>
+        <v>-0.1512515355033049</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8630468216742163</v>
+        <v>-0.4652380168219895</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9405019894715021</v>
+        <v>-0.4961828974275923</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.03167863060000484</v>
+        <v>-0.01929111461071549</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5982486394570345</v>
+        <v>-0.6255309421131154</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.088911006973213</v>
+        <v>-0.002219151198319252</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>30.9843852125372</v>
+        <v>47.20206000844619</v>
       </c>
       <c r="B35" t="n">
-        <v>64.32687189133024</v>
+        <v>93.64523329779884</v>
       </c>
       <c r="C35" t="n">
-        <v>33.71181665399202</v>
+        <v>38.58802367696237</v>
       </c>
       <c r="D35" t="n">
-        <v>5.128990948135627</v>
+        <v>7.005058513739492</v>
       </c>
       <c r="E35" t="n">
-        <v>2.647688677842523</v>
+        <v>3.676772005379448</v>
       </c>
       <c r="F35" t="n">
-        <v>1.818656736975655</v>
+        <v>2.951353811893232</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1925596967720744</v>
+        <v>0.0407498515375072</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2113210129866664</v>
+        <v>-0.7380322468848577</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4956850722892007</v>
+        <v>-0.7959087352554619</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5428979031710897</v>
+        <v>-0.8931265086888026</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.03031329793275233</v>
+        <v>-0.05610792749181601</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.6649912134171616</v>
+        <v>-0.5489463800534924</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.08939817814063845</v>
+        <v>-0.003872191291217908</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34.0658726394582</v>
+        <v>65.66596761026322</v>
       </c>
       <c r="B36" t="n">
-        <v>66.38672950709268</v>
+        <v>139.7307710370013</v>
       </c>
       <c r="C36" t="n">
-        <v>33.65782934510833</v>
+        <v>38.59964610944991</v>
       </c>
       <c r="D36" t="n">
-        <v>5.535251019193436</v>
+        <v>10.00070267357578</v>
       </c>
       <c r="E36" t="n">
-        <v>2.543257962191331</v>
+        <v>4.05263951002215</v>
       </c>
       <c r="F36" t="n">
-        <v>2.029830656558513</v>
+        <v>4.263961126172888</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1352317506799731</v>
+        <v>0.01364735235975932</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4041339358175832</v>
+        <v>-0.8985376884004028</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5963139982915993</v>
+        <v>-0.9148054573603706</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.6844340069461047</v>
+        <v>-0.968928197236835</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.03942121401165533</v>
+        <v>-0.1131359659457178</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.6495620366900169</v>
+        <v>-0.3428700192231254</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.07889407165677022</v>
+        <v>-0.006584092204978964</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>30.00519006780325</v>
+        <v>64.52282688942965</v>
       </c>
       <c r="B37" t="n">
-        <v>64.80140610832167</v>
+        <v>63.23167313452765</v>
       </c>
       <c r="C37" t="n">
-        <v>33.66944145721372</v>
+        <v>38.58810892877156</v>
       </c>
       <c r="D37" t="n">
-        <v>5.061538120935018</v>
+        <v>5.283875149577581</v>
       </c>
       <c r="E37" t="n">
-        <v>2.947544545046119</v>
+        <v>4.798822883438662</v>
       </c>
       <c r="F37" t="n">
-        <v>1.749722593272268</v>
+        <v>4.565987489113405</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2174734032595423</v>
+        <v>0.01331028649860019</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1324838886310179</v>
+        <v>-0.8951644830162838</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4565642500325907</v>
+        <v>-0.9128828577516604</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4814188332360758</v>
+        <v>-0.9679799336984727</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.00800671251975636</v>
+        <v>-0.1465021750947064</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.666299872102428</v>
+        <v>-0.658644570299721</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.08094183002200571</v>
+        <v>-0.003892083380031136</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>65.08945127596874</v>
+        <v>96.62923233179455</v>
       </c>
       <c r="B38" t="n">
-        <v>68.01771227367715</v>
+        <v>65.99256909218059</v>
       </c>
       <c r="C38" t="n">
-        <v>34.31164749550294</v>
+        <v>38.77763285469247</v>
       </c>
       <c r="D38" t="n">
-        <v>5.060278877981273</v>
+        <v>7.189301059483547</v>
       </c>
       <c r="E38" t="n">
-        <v>3.22509876223949</v>
+        <v>3.752684728275673</v>
       </c>
       <c r="F38" t="n">
-        <v>4.588045099142141</v>
+        <v>7.47825363789139</v>
       </c>
       <c r="G38" t="n">
-        <v>0.01315278289672195</v>
+        <v>0.003764733791488755</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9105157167472751</v>
+        <v>-0.9663818705081884</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9259364942773843</v>
+        <v>-0.9714518101157179</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9739370710532776</v>
+        <v>-0.9926373635567854</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.1658775712233821</v>
+        <v>-0.1654848807557877</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.6821979908578152</v>
+        <v>-0.5634832803640362</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.1373540808389812</v>
+        <v>-0.04811433276157656</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>35.21850051197474</v>
+        <v>45.06320901582373</v>
       </c>
       <c r="B39" t="n">
-        <v>65.44143777905759</v>
+        <v>74.12329055623412</v>
       </c>
       <c r="C39" t="n">
-        <v>33.66954048024102</v>
+        <v>38.59033668948315</v>
       </c>
       <c r="D39" t="n">
-        <v>5.271260226855762</v>
+        <v>7.477899083897317</v>
       </c>
       <c r="E39" t="n">
-        <v>2.847074608728684</v>
+        <v>4.835228360529142</v>
       </c>
       <c r="F39" t="n">
-        <v>2.088794144266096</v>
+        <v>2.822893007705114</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1189171453119442</v>
+        <v>0.04852755904530285</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.4603501419660497</v>
+        <v>-0.701005675954426</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6273576066265925</v>
+        <v>-0.7716250345002581</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7233337121308574</v>
+        <v>-0.8731878032422269</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.001822002677834765</v>
+        <v>-0.1769647406140428</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.6567372121736598</v>
+        <v>-0.5504213934388249</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.08096159094948768</v>
+        <v>-0.004411894212734552</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>66.41409102547884</v>
+        <v>71.6227690588469</v>
       </c>
       <c r="B40" t="n">
-        <v>154.0446538125715</v>
+        <v>88.55250409597305</v>
       </c>
       <c r="C40" t="n">
-        <v>33.67142750228356</v>
+        <v>39.05963384403758</v>
       </c>
       <c r="D40" t="n">
-        <v>9.760690143738532</v>
+        <v>8.636450809471334</v>
       </c>
       <c r="E40" t="n">
-        <v>4.187917056784267</v>
+        <v>4.204090736990093</v>
       </c>
       <c r="F40" t="n">
-        <v>4.276896889604827</v>
+        <v>4.688667136388061</v>
       </c>
       <c r="G40" t="n">
-        <v>0.013336331737966</v>
+        <v>0.01000440443090068</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9141097667694915</v>
+        <v>-0.9221234955044441</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9282503231038138</v>
+        <v>-0.9358533504244854</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9750011077490982</v>
+        <v>-0.9782229075751104</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.003783729809703631</v>
+        <v>-0.01415294132684768</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3711178910109333</v>
+        <v>-0.4121707679413518</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.08133816301315974</v>
+        <v>-0.1139145636087686</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>74.06647663711858</v>
+        <v>31.6683691979984</v>
       </c>
       <c r="B41" t="n">
-        <v>154.9386029528713</v>
+        <v>64.67990029392409</v>
       </c>
       <c r="C41" t="n">
-        <v>31.72814313042693</v>
+        <v>38.58093921942137</v>
       </c>
       <c r="D41" t="n">
-        <v>9.901837486017989</v>
+        <v>5.587168163923104</v>
       </c>
       <c r="E41" t="n">
-        <v>2.932766108367445</v>
+        <v>4.922985688060093</v>
       </c>
       <c r="F41" t="n">
-        <v>5.076433948113962</v>
+        <v>1.860505086855872</v>
       </c>
       <c r="G41" t="n">
-        <v>0.00920781668343832</v>
+        <v>0.1749672947278571</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.9371746597714284</v>
+        <v>-0.1512515355033049</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9487775018703586</v>
+        <v>-0.4652380168219895</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9833735411376646</v>
+        <v>-0.4961828974275923</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.1183905341704292</v>
+        <v>-0.01929111461071549</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4282817451302744</v>
+        <v>-0.6255309421131154</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.07898581789522773</v>
+        <v>-0.002219151198319252</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>76.15831403531098</v>
+        <v>82.41510602708476</v>
       </c>
       <c r="B42" t="n">
-        <v>128.7068589096673</v>
+        <v>77.61717836228885</v>
       </c>
       <c r="C42" t="n">
-        <v>34.32305821901062</v>
+        <v>38.60061884188559</v>
       </c>
       <c r="D42" t="n">
-        <v>8.772583497190915</v>
+        <v>8.116356667125729</v>
       </c>
       <c r="E42" t="n">
-        <v>2.332780589425889</v>
+        <v>4.064845855113639</v>
       </c>
       <c r="F42" t="n">
-        <v>5.152604506071695</v>
+        <v>5.78804202556553</v>
       </c>
       <c r="G42" t="n">
-        <v>0.008301811644443243</v>
+        <v>0.006250099695434859</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.9421082488756254</v>
+        <v>-0.9473592553896611</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.95296586409877</v>
+        <v>-0.9570353076600641</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.9850749998673604</v>
+        <v>-0.9868366217179099</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.008722167208435069</v>
+        <v>-0.02676369894285617</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.4439079163584687</v>
+        <v>-0.462207630442979</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.137744989703891</v>
+        <v>-0.006811063106638982</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>29.24009274351032</v>
+        <v>33.79236484283627</v>
       </c>
       <c r="B43" t="n">
-        <v>64.78725230411814</v>
+        <v>73.88924267734117</v>
       </c>
       <c r="C43" t="n">
-        <v>33.7139828992705</v>
+        <v>38.58512998584114</v>
       </c>
       <c r="D43" t="n">
-        <v>5.005046697793957</v>
+        <v>5.522281032728987</v>
       </c>
       <c r="E43" t="n">
-        <v>2.43575159631611</v>
+        <v>4.605554799802981</v>
       </c>
       <c r="F43" t="n">
-        <v>1.711791367298905</v>
+        <v>2.016492910348951</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2395503949507722</v>
+        <v>0.1365044129289471</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.06354707815110719</v>
+        <v>-0.3003130153175856</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.4231950445494972</v>
+        <v>-0.5407885395946963</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.4262391292257917</v>
+        <v>-0.6100594834631671</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.0724654563669513</v>
+        <v>-0.08087841595717686</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.6756665287677399</v>
+        <v>-0.6381421662543404</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.0898304716891753</v>
+        <v>-0.003196996696264859</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>55.00756388232132</v>
+        <v>97.19803955889226</v>
       </c>
       <c r="B44" t="n">
-        <v>63.33401122902397</v>
+        <v>84.00889130036543</v>
       </c>
       <c r="C44" t="n">
-        <v>33.67204810367539</v>
+        <v>38.5880410688911</v>
       </c>
       <c r="D44" t="n">
-        <v>5.964726984616892</v>
+        <v>7.045697936198727</v>
       </c>
       <c r="E44" t="n">
-        <v>3.164772742299614</v>
+        <v>4.059012957146646</v>
       </c>
       <c r="F44" t="n">
-        <v>3.596676392018525</v>
+        <v>7.534436173934728</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0236960595610484</v>
+        <v>0.003694522590508826</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.8541280906393988</v>
+        <v>-0.9669336691944699</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.8799156464388757</v>
+        <v>-0.9718973510721254</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9505633263113389</v>
+        <v>-0.9927938012611907</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.02326650037098502</v>
+        <v>-0.143671563238543</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.6122970662995838</v>
+        <v>-0.5675360318571073</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.08146200955102169</v>
+        <v>-0.003876249407922805</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>53.28023386625138</v>
+        <v>45.28628125976434</v>
       </c>
       <c r="B45" t="n">
-        <v>80.42840098807795</v>
+        <v>74.39144807762786</v>
       </c>
       <c r="C45" t="n">
-        <v>33.48743656630957</v>
+        <v>38.5903988730663</v>
       </c>
       <c r="D45" t="n">
-        <v>6.512605864260249</v>
+        <v>7.524351393172934</v>
       </c>
       <c r="E45" t="n">
-        <v>2.321150091630766</v>
+        <v>3.749623984729262</v>
       </c>
       <c r="F45" t="n">
-        <v>3.446458084093985</v>
+        <v>2.847536338238533</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02670751560551698</v>
+        <v>0.04767166700767821</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8397146685724703</v>
+        <v>-0.7053149634685404</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8687745438639609</v>
+        <v>-0.7744448331879568</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9440038121922255</v>
+        <v>-0.8755907752478552</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.04787006449277221</v>
+        <v>-0.1651399734769647</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.6037840552963801</v>
+        <v>-0.5443608281884682</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.05072483134827884</v>
+        <v>-0.004426403715470234</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>35.40457043776382</v>
+        <v>33.81498530470719</v>
       </c>
       <c r="B46" t="n">
-        <v>66.48275754171328</v>
+        <v>72.44071249604353</v>
       </c>
       <c r="C46" t="n">
-        <v>33.35833200555974</v>
+        <v>38.57160356115449</v>
       </c>
       <c r="D46" t="n">
-        <v>5.347504997434693</v>
+        <v>5.580662531348378</v>
       </c>
       <c r="E46" t="n">
-        <v>2.565737491487717</v>
+        <v>3.677426134182407</v>
       </c>
       <c r="F46" t="n">
-        <v>2.115049248548103</v>
+        <v>2.025152675241481</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1166490792951282</v>
+        <v>0.1362193732606126</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4686580740631512</v>
+        <v>-0.3016505481503128</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6320009597595941</v>
+        <v>-0.5414768028666864</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.7289357356160481</v>
+        <v>-0.6110240512821293</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.03060181709072525</v>
+        <v>-0.1005502215185528</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.6578955082739006</v>
+        <v>-0.6382764752466989</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.02981072429478818</v>
+        <v>-4.083093604764776e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50.34539962410602</v>
+        <v>94.24335036715715</v>
       </c>
       <c r="B47" t="n">
-        <v>69.71180991736816</v>
+        <v>111.1836289556671</v>
       </c>
       <c r="C47" t="n">
-        <v>33.67099198391923</v>
+        <v>38.58371381921108</v>
       </c>
       <c r="D47" t="n">
-        <v>6.540934490422266</v>
+        <v>7.216705101079031</v>
       </c>
       <c r="E47" t="n">
-        <v>3.219042363067085</v>
+        <v>3.660435276278951</v>
       </c>
       <c r="F47" t="n">
-        <v>3.19983889371885</v>
+        <v>7.155289836791086</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03268542546436862</v>
+        <v>0.004065333854502163</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.8108678347246897</v>
+        <v>-0.9639600447372585</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8472746541581976</v>
+        <v>-0.9695551864626224</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9304074617427793</v>
+        <v>-0.9919465262388243</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.01856142879417418</v>
+        <v>-0.1007785599720373</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5954582393449245</v>
+        <v>-0.5464838713659946</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.08125125144269227</v>
+        <v>-0.002866557815920656</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>49.95803979504198</v>
+        <v>49.18057944322017</v>
       </c>
       <c r="B48" t="n">
-        <v>69.72915372752813</v>
+        <v>110.1334650980478</v>
       </c>
       <c r="C48" t="n">
-        <v>33.67114313087787</v>
+        <v>38.61345641315383</v>
       </c>
       <c r="D48" t="n">
-        <v>6.540934490422266</v>
+        <v>7.511092667845229</v>
       </c>
       <c r="E48" t="n">
-        <v>3.377240564447729</v>
+        <v>4.934092193171952</v>
       </c>
       <c r="F48" t="n">
-        <v>3.162933654972144</v>
+        <v>3.193190884349936</v>
       </c>
       <c r="G48" t="n">
-        <v>0.03361181988256039</v>
+        <v>0.03523446824193131</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8065370629670917</v>
+        <v>-0.7676642325561323</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.8441133184734879</v>
+        <v>-0.8162023045070613</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9283025503811728</v>
+        <v>-0.9087200451679075</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.004524614146086198</v>
+        <v>-0.224828219552091</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5928964432793241</v>
+        <v>-0.5614770031403944</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0812814141651462</v>
+        <v>-0.009806496402562231</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>93.99519703331585</v>
+        <v>65.7381312818781</v>
       </c>
       <c r="B49" t="n">
-        <v>73.23980309911411</v>
+        <v>138.0159972709074</v>
       </c>
       <c r="C49" t="n">
-        <v>33.67331431036536</v>
+        <v>38.58436604716724</v>
       </c>
       <c r="D49" t="n">
-        <v>7.129704139529819</v>
+        <v>10.00070267357578</v>
       </c>
       <c r="E49" t="n">
-        <v>2.864427344895908</v>
+        <v>4.05263951002215</v>
       </c>
       <c r="F49" t="n">
-        <v>7.062731992934315</v>
+        <v>4.270182626935854</v>
       </c>
       <c r="G49" t="n">
-        <v>0.004165332998395201</v>
+        <v>0.0135947110337149</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.9680606070560372</v>
+        <v>-0.8988613068231477</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9727979059835015</v>
+        <v>-0.9150795222902675</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9931015052243249</v>
+        <v>-0.9690582235735388</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.08692934789548737</v>
+        <v>-0.1138464368703705</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.5771506761183528</v>
+        <v>-0.3433841853833813</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.08171469237905631</v>
+        <v>-0.003018744339021301</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>39.17807681838032</v>
+        <v>40.40391531605128</v>
       </c>
       <c r="B50" t="n">
-        <v>62.86157704056058</v>
+        <v>100.3009091305739</v>
       </c>
       <c r="C50" t="n">
-        <v>32.04819055813902</v>
+        <v>40.54022816217919</v>
       </c>
       <c r="D50" t="n">
-        <v>5.13381363162606</v>
+        <v>7.361637844141493</v>
       </c>
       <c r="E50" t="n">
-        <v>3.861742067728963</v>
+        <v>3.895202549036321</v>
       </c>
       <c r="F50" t="n">
-        <v>2.422897168579409</v>
+        <v>2.478666539270839</v>
       </c>
       <c r="G50" t="n">
-        <v>0.07957437652115364</v>
+        <v>0.07302499640244214</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.6064282625635856</v>
+        <v>-0.5847677204231672</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.712416352466807</v>
+        <v>-0.6983633080102506</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.8178125297144047</v>
+        <v>-0.8033651049575282</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.1248364783037221</v>
+        <v>-0.03095052641668977</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.6813858047652174</v>
+        <v>-0.5058914636683247</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.05685986653502229</v>
+        <v>-0.3515335720621394</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>30.0700055455638</v>
+        <v>89.17177196370893</v>
       </c>
       <c r="B51" t="n">
-        <v>64.33305441679752</v>
+        <v>71.03378376285583</v>
       </c>
       <c r="C51" t="n">
-        <v>33.67086608065684</v>
+        <v>38.75107688865761</v>
       </c>
       <c r="D51" t="n">
-        <v>5.002288602675328</v>
+        <v>7.410068578634437</v>
       </c>
       <c r="E51" t="n">
-        <v>3.331990064032555</v>
+        <v>3.947462407951313</v>
       </c>
       <c r="F51" t="n">
-        <v>1.761067912790779</v>
+        <v>6.525174939086018</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2153417918382012</v>
+        <v>0.004837017302366927</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1382427258600922</v>
+        <v>-0.9579102922310507</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4594186844263338</v>
+        <v>-0.9648978023433098</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.4860840054027846</v>
+        <v>-0.9901567618733758</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.05429364580237139</v>
+        <v>-0.01633964088653972</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.6737069653502257</v>
+        <v>-0.5103488752414261</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.08122612632476901</v>
+        <v>-0.04191794068677743</v>
       </c>
     </row>
   </sheetData>
